--- a/public/exports-from-60/29189625.xlsx
+++ b/public/exports-from-60/29189625.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258043</t>
+          <t xml:space="preserve">311258047</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -29839,7 +29839,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286988</t>
+          <t xml:space="preserve">311286996</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -30064,7 +30064,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286960</t>
+          <t xml:space="preserve">311286964</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">

--- a/public/exports-from-60/29189625.xlsx
+++ b/public/exports-from-60/29189625.xlsx
@@ -17389,7 +17389,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265936</t>
+          <t xml:space="preserve">311265937</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -29614,7 +29614,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286963</t>
+          <t xml:space="preserve">311286967</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286990</t>
+          <t xml:space="preserve">311287000</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">

--- a/public/exports-from-60/29189625.xlsx
+++ b/public/exports-from-60/29189625.xlsx
@@ -14539,7 +14539,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258047</t>
+          <t xml:space="preserve">311258043</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265937</t>
+          <t xml:space="preserve">311265936</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -29614,7 +29614,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286967</t>
+          <t xml:space="preserve">311286963</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -29839,7 +29839,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286996</t>
+          <t xml:space="preserve">311286988</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -30064,7 +30064,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286964</t>
+          <t xml:space="preserve">311286960</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287000</t>
+          <t xml:space="preserve">311286990</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
